--- a/AI_Trade_Record.xlsx
+++ b/AI_Trade_Record.xlsx
@@ -1,50 +1,532 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$8</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+  <si>
+    <t>时间</t>
+  </si>
+  <si>
+    <t>代码</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>阶段</t>
+  </si>
+  <si>
+    <t>评分</t>
+  </si>
+  <si>
+    <t>乖离率</t>
+  </si>
+  <si>
+    <t>量比</t>
+  </si>
+  <si>
+    <t>收益率</t>
+  </si>
+  <si>
+    <t>风险</t>
+  </si>
+  <si>
+    <t>交易建议</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:09</t>
+  </si>
+  <si>
+    <t>成都银行</t>
+  </si>
+  <si>
+    <t>起涨阶段</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:20</t>
+  </si>
+  <si>
+    <t>603368</t>
+  </si>
+  <si>
+    <t>柳药集团</t>
+  </si>
+  <si>
+    <t>西部大开发</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:07</t>
+  </si>
+  <si>
+    <t>和远气体</t>
+  </si>
+  <si>
+    <t>末端阶段</t>
+  </si>
+  <si>
+    <t>电池技术板块</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:23</t>
+  </si>
+  <si>
+    <t>603976</t>
+  </si>
+  <si>
+    <t>正川股份</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:12</t>
+  </si>
+  <si>
+    <t>沃顿科技</t>
+  </si>
+  <si>
+    <t>加速阶段</t>
+  </si>
+  <si>
+    <t>西部大开发板块</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:16</t>
+  </si>
+  <si>
+    <t>亚太实业</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:25</t>
+  </si>
+  <si>
+    <t>603257</t>
+  </si>
+  <si>
+    <t>中国瑞林</t>
+  </si>
+  <si>
+    <t>加速阶段黄金概念</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill/>
+  <fills count="36">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8CBAD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -53,94 +535,332 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -423,140 +1143,250 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="5" customWidth="1" min="9" max="9"/>
-    <col width="42" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
+    <col min="1" max="1" width="18.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667" customWidth="1"/>
+    <col min="3" max="3" width="13.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="9.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="5" customWidth="1"/>
+    <col min="6" max="6" width="12.4444444444444" customWidth="1"/>
+    <col min="7" max="7" width="11.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="9" max="9" width="11.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="11" max="11" width="18.3333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>代码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>阶段</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>评分</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>乖离率</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>量比</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>收益率</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>风险</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>交易建议</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-06-14 06:30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>末端阶段</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>601838</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>90</v>
+      </c>
+      <c r="F2">
+        <v>6.02</v>
+      </c>
+      <c r="G2">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3">
+        <v>90</v>
+      </c>
+      <c r="F3">
+        <v>2.59</v>
+      </c>
+      <c r="G3">
+        <v>1.36</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4">
+        <v>2971</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="n">
-        <v>909.52</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>863.64</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>[' 已盈利≥10% → 可分批止盈', ' 盈利≥20% → 高位风险区']</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2大尺寸</t>
-        </is>
+      <c r="E4">
+        <v>50</v>
+      </c>
+      <c r="F4">
+        <v>49.75</v>
+      </c>
+      <c r="G4">
+        <v>1.94</v>
+      </c>
+      <c r="K4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>20.47</v>
+      </c>
+      <c r="G5">
+        <v>1.56</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6">
+        <v>920</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>70</v>
+      </c>
+      <c r="F6">
+        <v>17.84</v>
+      </c>
+      <c r="G6">
+        <v>1.38</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7">
+        <v>70</v>
+      </c>
+      <c r="F7">
+        <v>13.17</v>
+      </c>
+      <c r="G7">
+        <v>1.25</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>90</v>
+      </c>
+      <c r="F8">
+        <v>8.88</v>
+      </c>
+      <c r="G8">
+        <v>1.54</v>
+      </c>
+      <c r="K8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K8" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:K8">
+      <sortCondition ref="D1" descending="1"/>
+    </sortState>
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AI_Trade_Record.xlsx
+++ b/AI_Trade_Record.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
   <si>
     <t>时间</t>
   </si>
@@ -65,46 +65,130 @@
     <t>备注</t>
   </si>
   <si>
+    <t>2026-06-14 17:20</t>
+  </si>
+  <si>
+    <t>603368</t>
+  </si>
+  <si>
+    <t>柳药集团</t>
+  </si>
+  <si>
+    <t>起涨阶段</t>
+  </si>
+  <si>
+    <t>西部大开发</t>
+  </si>
+  <si>
+    <t>2026-06-15 22:53</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>明天分红6毛</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:07</t>
+  </si>
+  <si>
+    <t>和远气体</t>
+  </si>
+  <si>
+    <t>末端阶段</t>
+  </si>
+  <si>
+    <t>电池技术板块</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:23</t>
+  </si>
+  <si>
+    <t>603976</t>
+  </si>
+  <si>
+    <t>正川股份</t>
+  </si>
+  <si>
+    <t>2026-06-16 23:03</t>
+  </si>
+  <si>
+    <t>观察</t>
+  </si>
+  <si>
     <t>2026-06-14 17:09</t>
   </si>
   <si>
     <t>成都银行</t>
   </si>
   <si>
-    <t>起涨阶段</t>
-  </si>
-  <si>
-    <t>2026-06-14 17:20</t>
-  </si>
-  <si>
-    <t>603368</t>
-  </si>
-  <si>
-    <t>柳药集团</t>
-  </si>
-  <si>
-    <t>西部大开发</t>
-  </si>
-  <si>
-    <t>2026-06-14 17:07</t>
-  </si>
-  <si>
-    <t>和远气体</t>
-  </si>
-  <si>
-    <t>末端阶段</t>
-  </si>
-  <si>
-    <t>电池技术板块</t>
-  </si>
-  <si>
-    <t>2026-06-14 17:23</t>
-  </si>
-  <si>
-    <t>603976</t>
-  </si>
-  <si>
-    <t>正川股份</t>
+    <t>2026-06-15 22:50</t>
+  </si>
+  <si>
+    <t>601838</t>
+  </si>
+  <si>
+    <t>今日买入</t>
+  </si>
+  <si>
+    <t>2026-06-16 23:01</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:25</t>
+  </si>
+  <si>
+    <t>603257</t>
+  </si>
+  <si>
+    <t>中国瑞林</t>
+  </si>
+  <si>
+    <t>加速阶段</t>
+  </si>
+  <si>
+    <t>加速阶段黄金概念</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:47</t>
+  </si>
+  <si>
+    <t>000691</t>
+  </si>
+  <si>
+    <t>亚太实业</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:56</t>
+  </si>
+  <si>
+    <t>002522</t>
+  </si>
+  <si>
+    <t>浙江众成</t>
+  </si>
+  <si>
+    <t>观察游资打架</t>
+  </si>
+  <si>
+    <t>2026-06-14 17:16</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:43</t>
+  </si>
+  <si>
+    <t>002937</t>
+  </si>
+  <si>
+    <t>兴瑞科技</t>
+  </si>
+  <si>
+    <t>通信</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:53</t>
   </si>
   <si>
     <t>2026-06-14 17:12</t>
@@ -113,28 +197,37 @@
     <t>沃顿科技</t>
   </si>
   <si>
-    <t>加速阶段</t>
-  </si>
-  <si>
     <t>西部大开发板块</t>
   </si>
   <si>
-    <t>2026-06-14 17:16</t>
-  </si>
-  <si>
-    <t>亚太实业</t>
-  </si>
-  <si>
-    <t>2026-06-14 17:25</t>
-  </si>
-  <si>
-    <t>603257</t>
-  </si>
-  <si>
-    <t>中国瑞林</t>
-  </si>
-  <si>
-    <t>加速阶段黄金概念</t>
+    <t>2026-06-15 21:51</t>
+  </si>
+  <si>
+    <t>000630</t>
+  </si>
+  <si>
+    <t>铜陵有色</t>
+  </si>
+  <si>
+    <t>通信5g</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:45</t>
+  </si>
+  <si>
+    <t>盛和资源</t>
+  </si>
+  <si>
+    <t>苹果概念</t>
+  </si>
+  <si>
+    <t>2026-06-15 21:49</t>
+  </si>
+  <si>
+    <t>002258</t>
+  </si>
+  <si>
+    <t>利尔化学</t>
   </si>
 </sst>
 </file>
@@ -1148,21 +1241,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="7"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="9.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="13.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="9.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="4" width="9.66666666666667" customWidth="1"/>
     <col min="5" max="5" width="5" customWidth="1"/>
-    <col min="6" max="6" width="12.4444444444444" customWidth="1"/>
-    <col min="7" max="7" width="11.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
-    <col min="9" max="9" width="11.3333333333333" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
-    <col min="11" max="11" width="18.3333333333333" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="8" customWidth="1"/>
+    <col min="9" max="9" width="5" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1204,63 +1296,75 @@
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
-        <v>601838</v>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2">
         <v>90</v>
       </c>
       <c r="F2">
-        <v>6.02</v>
+        <v>2.59</v>
       </c>
       <c r="G2">
-        <v>1.16</v>
+        <v>1.36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="E3">
         <v>90</v>
       </c>
       <c r="F3">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>1.36</v>
+        <v>1.15</v>
+      </c>
+      <c r="H3">
+        <v>4.04</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" hidden="1" spans="1:11">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>2971</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E4">
         <v>50</v>
@@ -1272,21 +1376,21 @@
         <v>1.94</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" hidden="1" spans="1:11">
       <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="E5">
         <v>50</v>
@@ -1298,30 +1402,39 @@
         <v>1.56</v>
       </c>
       <c r="K5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
-        <v>920</v>
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>27</v>
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F6">
-        <v>17.84</v>
+        <v>2.32</v>
       </c>
       <c r="G6">
-        <v>1.38</v>
+        <v>1.05</v>
+      </c>
+      <c r="H6">
+        <v>-4.79</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
       </c>
       <c r="K6" t="s">
         <v>28</v>
@@ -1331,26 +1444,23 @@
       <c r="A7" t="s">
         <v>29</v>
       </c>
-      <c r="B7" t="s">
-        <v>30</v>
+      <c r="B7">
+        <v>601838</v>
       </c>
       <c r="C7" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>27</v>
+      <c r="D7" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="E7">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="F7">
-        <v>13.17</v>
+        <v>6.02</v>
       </c>
       <c r="G7">
-        <v>1.25</v>
-      </c>
-      <c r="K7" t="s">
-        <v>17</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1361,27 +1471,328 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8">
+        <v>70</v>
+      </c>
+      <c r="F8">
+        <v>5.37</v>
+      </c>
+      <c r="G8">
+        <v>0.9</v>
+      </c>
+      <c r="H8">
+        <v>0.45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8">
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9">
+        <v>70</v>
+      </c>
+      <c r="F9">
+        <v>2.52</v>
+      </c>
+      <c r="G9">
+        <v>0.86</v>
+      </c>
+      <c r="H9">
+        <v>-1.96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10">
         <v>90</v>
       </c>
-      <c r="F8">
+      <c r="F10">
         <v>8.88</v>
       </c>
-      <c r="G8">
+      <c r="G10">
         <v>1.54</v>
       </c>
-      <c r="K8" t="s">
-        <v>34</v>
+      <c r="K10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" hidden="1" spans="1:11">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11">
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>18.09</v>
+      </c>
+      <c r="G11">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12">
+        <v>90</v>
+      </c>
+      <c r="F12">
+        <v>9.12</v>
+      </c>
+      <c r="G12">
+        <v>1.61</v>
+      </c>
+      <c r="K12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+      <c r="F13">
+        <v>13.17</v>
+      </c>
+      <c r="G13">
+        <v>1.25</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14">
+        <v>70</v>
+      </c>
+      <c r="F14">
+        <v>16.15</v>
+      </c>
+      <c r="G14">
+        <v>1.56</v>
+      </c>
+      <c r="K14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <v>70</v>
+      </c>
+      <c r="F15">
+        <v>16.15</v>
+      </c>
+      <c r="G15">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16">
+        <v>920</v>
+      </c>
+      <c r="C16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E16">
+        <v>70</v>
+      </c>
+      <c r="F16">
+        <v>17.84</v>
+      </c>
+      <c r="G16">
+        <v>1.38</v>
+      </c>
+      <c r="K16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="s">
+        <v>58</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17">
+        <v>70</v>
+      </c>
+      <c r="F17">
+        <v>16.95</v>
+      </c>
+      <c r="G17">
+        <v>1.97</v>
+      </c>
+      <c r="K17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18">
+        <v>70</v>
+      </c>
+      <c r="F18">
+        <v>12.39</v>
+      </c>
+      <c r="G18">
+        <v>1.29</v>
+      </c>
+      <c r="K18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19">
+        <v>90</v>
+      </c>
+      <c r="F19">
+        <v>9</v>
+      </c>
+      <c r="G19">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K8" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:K8">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K19" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="加速阶段"/>
+        <filter val="起涨阶段"/>
+      </filters>
+    </filterColumn>
+    <sortState ref="A2:K19">
       <sortCondition ref="D1" descending="1"/>
     </sortState>
     <extLst/>
